--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488149_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488149_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. NAVARRO GARRIDO</t>
+          <t>P. SECO LOPEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7402</v>
+        <v>6.5852</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5045</v>
+        <v>3.5313</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2357</v>
+        <v>3.0539</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9832</v>
+        <v>3.8937</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1382</v>
+        <v>4.462</v>
       </c>
       <c r="I2" t="n">
-        <v>0.845</v>
+        <v>-0.5683</v>
       </c>
       <c r="J2" t="n">
-        <v>4.878</v>
+        <v>3.1388</v>
       </c>
       <c r="K2" t="n">
-        <v>4.878</v>
+        <v>3.7917</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0.6529</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1052</v>
+        <v>0.7549</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7398</v>
+        <v>0.6703</v>
       </c>
       <c r="O2" t="n">
-        <v>0.845</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1499</v>
+        <v>2.594</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1455</v>
+        <v>-0.1085</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9066</v>
+        <v>0.0606</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7611</v>
+        <v>-0.1691</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3144</v>
+        <v>1.1324</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5727</v>
+        <v>1.2583</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2583</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. SECO LOPEZ</t>
+          <t>S. NAVARRO GARRIDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3231</v>
+        <v>6.2872</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2693</v>
+        <v>4.9284</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0539</v>
+        <v>1.3588</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8937</v>
+        <v>4.9832</v>
       </c>
       <c r="H3" t="n">
-        <v>4.462</v>
+        <v>4.1382</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5683</v>
+        <v>0.845</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1388</v>
+        <v>4.878</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7917</v>
+        <v>4.878</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7549</v>
+        <v>0.1052</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6703</v>
+        <v>-0.7398</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R3" t="n">
-        <v>2.594</v>
+        <v>3.1499</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3706</v>
+        <v>-0.3075</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2014</v>
+        <v>0.3305</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1691</v>
+        <v>-0.638</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1324</v>
+        <v>0.3144</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2583</v>
+        <v>1.5727</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1259</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.048</v>
+        <v>2.7548</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4429</v>
+        <v>2.0512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6051</v>
+        <v>0.7036</v>
       </c>
       <c r="G4" t="n">
         <v>1.8659</v>
@@ -766,13 +766,13 @@
         <v>1.297</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0109</v>
+        <v>-0.2823</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1269</v>
+        <v>-0.2649</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1159</v>
+        <v>-0.0174</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1259</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3221</v>
+        <v>0.9846</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3221</v>
+        <v>-0.7975</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.7821</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3221</v>
+        <v>-0.5363</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3221</v>
+        <v>0.0319</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.5683</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3221</v>
+        <v>-0.7864</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3221</v>
+        <v>1.1722</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.9586</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.1403</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.3903</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.6644</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.3435</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.3209</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1885</v>
+        <v>0.3221</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3965</v>
+        <v>0.3221</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5851</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5363</v>
+        <v>0.3221</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0319</v>
+        <v>0.3221</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5683</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7864</v>
+        <v>0.3221</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1722</v>
+        <v>0.3221</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9586</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1403</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3903</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4604</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9426</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5178</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. POL RUBIO</t>
+          <t>I. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1323</v>
+        <v>-0.5959</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6129</v>
+        <v>-1.9548</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4806</v>
+        <v>1.3589</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2989</v>
+        <v>-1.0192</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1683</v>
+        <v>-0.5815</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1306</v>
+        <v>-0.4377</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6529</v>
+        <v>-1.1212</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.4683</v>
       </c>
       <c r="L7" t="n">
         <v>-0.6529</v>
       </c>
       <c r="M7" t="n">
-        <v>0.354</v>
+        <v>0.102</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1683</v>
+        <v>-0.1131</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5223</v>
+        <v>0.2152</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.093</v>
+        <v>-0.3211</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0336</v>
+        <v>-0.2216</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1266</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1886</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. VIOQUE LOMBARDO</t>
+          <t>D. POL RUBIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1348</v>
+        <v>-1.1569</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4445</v>
+        <v>-1.6129</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3097</v>
+        <v>0.456</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0192</v>
+        <v>-0.2989</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5815</v>
+        <v>-0.1683</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4377</v>
+        <v>-0.1306</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1212</v>
+        <v>-0.6529</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4683</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6529</v>
       </c>
       <c r="M8" t="n">
-        <v>0.102</v>
+        <v>0.354</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1131</v>
+        <v>-0.1683</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2152</v>
+        <v>0.5223</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.86</v>
+        <v>0.0684</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7113</v>
+        <v>-0.0336</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1487</v>
+        <v>0.102</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1886</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7318</v>
+        <v>-2.9469</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7972</v>
+        <v>-1.9383</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9347</v>
+        <v>-1.0085</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1172</v>
@@ -1156,13 +1156,13 @@
         <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>0.473</v>
+        <v>0.258</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1057</v>
+        <v>-0.0354</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3673</v>
+        <v>0.2935</v>
       </c>
       <c r="V9" t="n">
         <v>-2.0142</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8898</v>
+        <v>-3.444</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.5348</v>
+        <v>-4.9904</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6449</v>
+        <v>1.5464</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5987</v>
@@ -1234,13 +1234,13 @@
         <v>2.594</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6661</v>
+        <v>-1.2202</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3679</v>
+        <v>-0.8235</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2982</v>
+        <v>-0.3967</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4398</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5638</v>
+        <v>-7.4063</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.798500000000001</v>
+        <v>-10.124</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2348</v>
+        <v>2.7177</v>
       </c>
       <c r="G11" t="n">
         <v>-5.313</v>
@@ -1312,13 +1312,13 @@
         <v>2.9646</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4337</v>
+        <v>-0.4088</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1231</v>
+        <v>-0.2024</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3106</v>
+        <v>-0.2065</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9433</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.3012</v>
+        <v>-7.695</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.8185</v>
+        <v>-8.458399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5172</v>
+        <v>0.7634</v>
       </c>
       <c r="G12" t="n">
         <v>-7.2138</v>
@@ -1390,13 +1390,13 @@
         <v>2.594</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8841</v>
+        <v>-0.2779</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3991</v>
+        <v>-0.0391</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.485</v>
+        <v>-0.2388</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9444</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.131800000000002</v>
+        <v>-6.311099999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.8641</v>
+        <v>-19.0433</v>
       </c>
       <c r="F13" t="n">
         <v>12.7323</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.032200000000002</v>
+        <v>-7.032200000000001</v>
       </c>
       <c r="H13" t="n">
         <v>5.179200000000001</v>
@@ -1468,13 +1468,13 @@
         <v>19.4551</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.0851</v>
+        <v>-3.2643</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3936</v>
+        <v>-1.5729</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6913</v>
+        <v>-1.6914</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5733</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0687</v>
+        <v>6.0264</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9619</v>
+        <v>2.0598</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1068</v>
+        <v>3.9665</v>
       </c>
       <c r="G14" t="n">
         <v>2.258</v>
@@ -1546,13 +1546,13 @@
         <v>1.297</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1077</v>
+        <v>1.0654</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0074</v>
+        <v>0.0905</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1152</v>
+        <v>0.9749</v>
       </c>
       <c r="V14" t="n">
         <v>2.5177</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1972</v>
+        <v>4.0237</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3656</v>
+        <v>2.5615</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8315</v>
+        <v>1.4622</v>
       </c>
       <c r="G15" t="n">
         <v>2.6438</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3681</v>
+        <v>0.1946</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0174</v>
+        <v>0.2133</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3506</v>
+        <v>-0.0187</v>
       </c>
       <c r="V15" t="n">
         <v>0.6294</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6502</v>
+        <v>2.7149</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9508</v>
+        <v>-2.0487</v>
       </c>
       <c r="F16" t="n">
-        <v>4.601</v>
+        <v>4.7636</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3053</v>
@@ -1702,13 +1702,13 @@
         <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6231</v>
+        <v>1.6878</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6666</v>
+        <v>0.5686</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9565</v>
+        <v>1.1192</v>
       </c>
       <c r="V16" t="n">
         <v>2.5177</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5983</v>
+        <v>1.6962</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4801</v>
+        <v>-0.1762</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0784</v>
+        <v>1.8724</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0772</v>
+        <v>3.6022</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5726</v>
+        <v>0.9969</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6498</v>
+        <v>2.6053</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7683</v>
+        <v>1.9918</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1984</v>
+        <v>2.5202</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5699</v>
+        <v>-0.5284</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8455</v>
+        <v>1.6105</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3743</v>
+        <v>-1.5233</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2197</v>
+        <v>3.1337</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1117</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9646</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>2.2234</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9827</v>
+        <v>0.7234</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9737</v>
+        <v>0.4822</v>
       </c>
       <c r="U17" t="n">
-        <v>1.009</v>
+        <v>0.2412</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5733</v>
+        <v>-1.8883</v>
       </c>
       <c r="W17" t="n">
         <v>0.3144</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8877</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3842</v>
+        <v>1.2222</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1176</v>
+        <v>1.2394</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2666</v>
+        <v>-0.0172</v>
       </c>
       <c r="G18" t="n">
-        <v>3.6022</v>
+        <v>2.3351</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9969</v>
+        <v>-0.3975</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6053</v>
+        <v>2.7326</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9918</v>
+        <v>2.0565</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5202</v>
+        <v>0.1074</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5284</v>
+        <v>1.9492</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6105</v>
+        <v>0.2786</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5233</v>
+        <v>-0.5048</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1337</v>
+        <v>0.7834</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9646</v>
+        <v>-0.1853</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2234</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4114</v>
+        <v>-0.5391</v>
       </c>
       <c r="T18" t="n">
-        <v>0.776</v>
+        <v>-0.0019</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3646</v>
+        <v>-0.5372</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8883</v>
+        <v>-0.9444</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2027</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8786</v>
+        <v>0.977</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0435</v>
+        <v>-1.1656</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1649</v>
+        <v>2.1426</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3351</v>
+        <v>0.0772</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3975</v>
+        <v>-1.5726</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7326</v>
+        <v>1.6498</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0565</v>
+        <v>-1.7683</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1074</v>
+        <v>-1.1984</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9492</v>
+        <v>-0.5699</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2786</v>
+        <v>1.8455</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5048</v>
+        <v>-0.3743</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7834</v>
+        <v>2.2197</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8827</v>
+        <v>1.3614</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1977</v>
+        <v>0.2882</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6849</v>
+        <v>1.0732</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9444</v>
+        <v>-1.5733</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. GARCIA FERNANDEZ</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0441</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2583</v>
+        <v>-0.7447</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3023</v>
+        <v>0.7531</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1842</v>
+        <v>0.4222</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2257</v>
+        <v>-0.2721</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0415</v>
+        <v>0.6943</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.547</v>
+        <v>0.1059</v>
       </c>
       <c r="K21" t="n">
         <v>0.0644</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.0415</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3627</v>
+        <v>0.3163</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2901</v>
+        <v>-0.3366</v>
       </c>
       <c r="O21" t="n">
         <v>0.6529</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3706</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5989</v>
+        <v>-0.1729</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2151</v>
+        <v>0.0759</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3837</v>
+        <v>-0.2487</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>M. GARCIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.201</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7447</v>
+        <v>-1.4541</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7531</v>
+        <v>1.2531</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4222</v>
+        <v>-0.1842</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2721</v>
+        <v>-0.2257</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6943</v>
+        <v>0.0415</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1059</v>
+        <v>-0.547</v>
       </c>
       <c r="K22" t="n">
         <v>0.0644</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3163</v>
+        <v>0.3627</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3366</v>
+        <v>-0.2901</v>
       </c>
       <c r="O22" t="n">
         <v>0.6529</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1729</v>
+        <v>0.3538</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0759</v>
+        <v>0.0193</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2487</v>
+        <v>0.3345</v>
       </c>
       <c r="V22" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8398</v>
+        <v>-3.9241</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.5811</v>
+        <v>-7.0914</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7413</v>
+        <v>3.1673</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3967</v>
@@ -2248,13 +2248,13 @@
         <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.3255</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2773</v>
+        <v>0.2124</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3129</v>
+        <v>0.1131</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9886</v>
+        <v>-4.2367</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.5204</v>
+        <v>-6.2266</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5318</v>
+        <v>1.9899</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5506</v>
@@ -2326,13 +2326,13 @@
         <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3611</v>
+        <v>0.3908</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.2571</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1897</v>
+        <v>0.6479</v>
       </c>
       <c r="V24" t="n">
         <v>-0.0005</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.132</v>
+        <v>8.437700000000003</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.0468</v>
+        <v>-13.0466</v>
       </c>
       <c r="F25" t="n">
-        <v>20.1785</v>
+        <v>21.4841</v>
       </c>
       <c r="G25" t="n">
         <v>7.032299999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.1792</v>
+        <v>-5.179200000000001</v>
       </c>
       <c r="I25" t="n">
         <v>12.2114</v>
@@ -2380,7 +2380,7 @@
         <v>-2.8338</v>
       </c>
       <c r="K25" t="n">
-        <v>3.887600000000001</v>
+        <v>3.8876</v>
       </c>
       <c r="L25" t="n">
         <v>-6.721399999999999</v>
@@ -2389,7 +2389,7 @@
         <v>9.866</v>
       </c>
       <c r="N25" t="n">
-        <v>-9.0669</v>
+        <v>-9.066899999999999</v>
       </c>
       <c r="O25" t="n">
         <v>18.933</v>
@@ -2404,13 +2404,13 @@
         <v>13.8966</v>
       </c>
       <c r="S25" t="n">
-        <v>4.084999999999999</v>
+        <v>5.390699999999999</v>
       </c>
       <c r="T25" t="n">
         <v>1.6914</v>
       </c>
       <c r="U25" t="n">
-        <v>2.393600000000001</v>
+        <v>3.699400000000001</v>
       </c>
       <c r="V25" t="n">
         <v>1.5733</v>
